--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -1,64 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_automation\test-automation-playwright\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0A1B14-3D88-4ADE-8DBC-BECEA899E757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name=" Test cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Input length type</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Expected output</t>
+  </si>
+  <si>
+    <t>Actual output</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>POS_001</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>oya koheda yanne?</t>
+  </si>
+  <si>
+    <t>ඔයා කොහෙද යන්නේ?</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="8.5"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="8"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <color theme="1"/>
-      <sz val="8"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -105,114 +145,46 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -478,142 +450,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="10.88671875" customWidth="1" min="1" max="1"/>
-    <col width="22.109375" customWidth="1" min="3" max="3"/>
-    <col width="25.33203125" customWidth="1" min="4" max="4"/>
-    <col width="22.5546875" customWidth="1" min="5" max="5"/>
-    <col width="14.33203125" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12.33203125" customWidth="1" min="9" max="10"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Input length type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Expected output</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Actual output</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="49.95" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>POS_001</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>oyata kohomada</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාට කොහොමද</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාට කොහොමද</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="49.95" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="49.95" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="49.95" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="49.95" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="49.95" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="49.95" customHeight="1">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="49.95" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -1,104 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_automation\test-automation-playwright\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0A1B14-3D88-4ADE-8DBC-BECEA899E757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
+    <sheet name=" Test cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Input length type</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Expected output</t>
-  </si>
-  <si>
-    <t>Actual output</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>POS_001</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>oya koheda yanne?</t>
-  </si>
-  <si>
-    <t>ඔයා කොහෙද යන්නේ?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8.5"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -145,46 +105,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -450,125 +478,1644 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F105"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col width="10.88671875" customWidth="1" min="1" max="1"/>
+    <col width="33.5546875" customWidth="1" min="3" max="3"/>
+    <col width="28.21875" customWidth="1" min="4" max="4"/>
+    <col width="29.109375" customWidth="1" min="5" max="5"/>
+    <col width="13.33203125" customWidth="1" min="6" max="6"/>
+    <col width="12.33203125" customWidth="1" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+    <row r="1" ht="36.6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input length type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected output</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Actual output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="49.95" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Neg_001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Mama heta panadura yanawa, so complete this today.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>මම හෙට පානදුර යනවා, so complete this today.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="49.95" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="49.95" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="49.95" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="49.95" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Neg_002</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Bath kawata passe sellam karanna puluwanda?</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>බත් කෑවට පස්සේ සෙල්ලම් කරන්න පුලුවන්ද?</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="49.95" customHeight="1">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="49.95" customHeight="1">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="49.95" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="49.95" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Neg_003</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ikmanata adumak anda ganna gamanak yanna, man eddi lasthi wela inna.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>ඉක්මනට ඇඳුමක් ඇද ගන්න ගමනක් යන්න, මං එද්දි ලෑස්ති වෙලා ඉන්න.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="49.95" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="49.95" customHeight="1">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13" ht="49.95" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="49.95" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Neg_004</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Rata kama one nam pallayahata enna</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>රෑට කෑම ඕනේ නම් පල්ලයහට එන්න</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49.95" customHeight="1">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="49.95" customHeight="1">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="49.95" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="49.95" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Neg_005</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Ayubovan! Obawa sadharayen piliganimu.</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ආයුබෝවන්! ඔබව සාදරයෙන් පිළිගනිමු.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49.95" customHeight="1">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="49.95" customHeight="1">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="49.95" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="49.95" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Neg_006</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Hodin vibagaya karanna.</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>හොඳින් විභාගය කරන්න.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="49.95" customHeight="1">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="49.95" customHeight="1">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="49.95" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="49.95" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Neg_007</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ada rata eddi mata sarungalayak genna puluwandha?.</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>අද රෑට එද්දි මට සරුංගලයක් ගේන්න පුලුවන්ද?</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>අඩ රට එඩ්ඩි මට සරුන්ගලයක් ගෙන්න පුලුwඅන්ද?.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="49.95" customHeight="1">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="49.95" customHeight="1">
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="49.95" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="49.95" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Neg_008</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Mata sapattu dekak aran dennako iridata kalin?</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>මට සපත්තු දෙකක් අරන් දෙන්නකෝ ඉරිදට කලින්?</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>මට සපත්තු දෙකක් අරන් දෙන්නකෝ ඉරිදාට කලින්?</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.95" customHeight="1">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="49.95" customHeight="1">
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="49.95" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="49.95" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Neg_009</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ane hari nande mn gedara gihin balannam.</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>අනේ හරි නැන්දේ  මන් ගෙදර ගිහින් බලන්නම්.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>අනේ හරි නන්දේ මන් ගෙදර ගිහින් බලන්නම්.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="49.95" customHeight="1">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="49.95" customHeight="1">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="49.95" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="49.95" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Neg_010</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Hari mn welapaha bus eke gedara ennam.</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>හරි මන් වෙලපහ බස් එකේ ගෙදර එන්නම්.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>හරි මන් වෙලාපහ බස් එකේ ගෙදර එන්නම්.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="49.95" customHeight="1">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="49.95" customHeight="1">
+      <c r="A40" s="3" t="n"/>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+    </row>
+    <row r="41" ht="49.95" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="49.95" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Neg_011</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Katha katha kara kara inna epa.</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>කතා කතා කර කර ඉන්න එපා.</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ඛත කත කර කර ඉන්න එප.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="49.95" customHeight="1">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="49.95" customHeight="1">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+    </row>
+    <row r="45" ht="49.95" customHeight="1">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="49.95" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Neg_012</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Dhenna dhenna katha karanna.</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>දෙන්නා දෙන්නා කතා කරන්න.</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>දැහෙන්න දෙන්න කතා කරන්න.</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="49.95" customHeight="1">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+    </row>
+    <row r="48" ht="49.95" customHeight="1">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+    </row>
+    <row r="49" ht="49.95" customHeight="1">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+    </row>
+    <row r="50" ht="49.95" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Neg_013</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Adha wassa wahiwidha?</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>අද වැස්ස වහීවිද?</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>අද වැස්ස වහියි?</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="49.95" customHeight="1">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+    </row>
+    <row r="52" ht="49.95" customHeight="1">
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+    </row>
+    <row r="53" ht="49.95" customHeight="1">
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="49.95" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Neg_014</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Mata udawu karanna; mata amaruyi.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>මට උදව් කරන්න; මට අමාරුයි.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>මට උදවු කරන්න; මට අමාරුයි.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="49.95" customHeight="1">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+    </row>
+    <row r="56" ht="49.95" customHeight="1">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+    </row>
+    <row r="57" ht="49.95" customHeight="1">
+      <c r="A57" s="4" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+    </row>
+    <row r="58" ht="49.95" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Neg_015</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>wenam namk dagnn.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>වෙනම නමක් දාගන්න.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>වෙනම් නමක් දාගන්න.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="49.95" customHeight="1">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="49.95" customHeight="1">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+    </row>
+    <row r="61" ht="49.95" customHeight="1">
+      <c r="A61" s="4" t="n"/>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+    </row>
+    <row r="62" ht="49.95" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Neg_016</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>ona mgulak karaganna.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>ඕන මගුලක් කරගන්න.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ඕන මෘගුලක් කරගන්න.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="49.95" customHeight="1">
+      <c r="A63" s="3" t="n"/>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="49.95" customHeight="1">
+      <c r="A64" s="3" t="n"/>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+    </row>
+    <row r="65" ht="49.95" customHeight="1">
+      <c r="A65" s="4" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="49.95" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Neg_017</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Mage mobile phone eka charge karannako.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>මගේ mobile phone එක charge කරන්නකො.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>මගේ mobile phone එක charge කරන්නකෝ.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="49.95" customHeight="1">
+      <c r="A67" s="3" t="n"/>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+    </row>
+    <row r="68" ht="49.95" customHeight="1">
+      <c r="A68" s="3" t="n"/>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+    </row>
+    <row r="69" ht="49.95" customHeight="1">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+    </row>
+    <row r="70" ht="49.95" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Neg_018</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>iridata climate eka godak hot.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>ඉරිදට climate එක ගොඩක් hot.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>අද climate එක ගොඩක් hot.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="49.95" customHeight="1">
+      <c r="A71" s="3" t="n"/>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="49.95" customHeight="1">
+      <c r="A72" s="3" t="n"/>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+    </row>
+    <row r="73" ht="49.95" customHeight="1">
+      <c r="A73" s="4" t="n"/>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="49.95" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Neg_019</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Karunakarala meka keep in mind thiyaganna.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>කරුණාකරලා මේක keep in mind තියාගන්න.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ඛරුනකරල මෙක කේප් ඉන් මින්ඩ් තියගන්න.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="49.95" customHeight="1">
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+    </row>
+    <row r="76" ht="49.95" customHeight="1">
+      <c r="A76" s="3" t="n"/>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+    </row>
+    <row r="77" ht="49.95" customHeight="1">
+      <c r="A77" s="4" t="n"/>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="49.95" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>Neg_020</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Mama hithanne api on the right track inne.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>මම හිතන්නේ අපි on the right track ඉන්නේ.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>කරුණාකරලා මේක කීප් ඉන් මින්ඩ් තියාගන්න.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="49.95" customHeight="1">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+    </row>
+    <row r="80" ht="49.95" customHeight="1">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="3" t="n"/>
+      <c r="C80" s="3" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+    </row>
+    <row r="81" ht="49.95" customHeight="1">
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+    </row>
+    <row r="82" ht="49.95" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Neg_021</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Mage email ekata reply karanna.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>මගේ email එකට reply කරන්න.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>මම හිතන්නේ අපි on the right track ඉන්නේ.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="49.95" customHeight="1">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+    </row>
+    <row r="84" ht="49.95" customHeight="1">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+    </row>
+    <row r="85" ht="49.95" customHeight="1">
+      <c r="A85" s="4" t="n"/>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+    </row>
+    <row r="86" ht="49.95" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>Neg_022</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Oyage username eka mokakda?</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>ඔයාගේ username එක මොකක්ද?</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>මගේ email එකට reply කරන්න.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="49.95" customHeight="1">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="49.95" customHeight="1">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+    </row>
+    <row r="89" ht="49.95" customHeight="1">
+      <c r="A89" s="4" t="n"/>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="49.95" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Neg_023</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Mage project eka GitHub ekata dammiya.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>මගේ project එක GitHub එකට දැම්මා.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ඔයාගේ username එක මොකක්ද?</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="49.95" customHeight="1">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+    </row>
+    <row r="92" ht="49.95" customHeight="1">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+    </row>
+    <row r="93" ht="49.95" customHeight="1">
+      <c r="A93" s="4" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="49.95" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Neg_024</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Mama Instagram ekata photo ekak damma.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>මම Instagram එකට photo එකක් දැම්මා.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>මම Instagram එකට photo එකක් දැම්මා.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="49.95" customHeight="1">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="3" t="n"/>
+      <c r="C95" s="3" t="n"/>
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+    </row>
+    <row r="96" ht="49.95" customHeight="1">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="3" t="n"/>
+      <c r="C96" s="3" t="n"/>
+      <c r="D96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n"/>
+    </row>
+    <row r="97" ht="49.95" customHeight="1">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+    </row>
+    <row r="98" ht="49.95" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Neg_025</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>SMS ekak ewanna, mama busy inne.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>SMS එකක් එවන්න, මම busy ඉන්නේ.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>SMS එකක් එwඅන්න, මම බුස්ය් ඉන්නේ.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="49.95" customHeight="1">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="3" t="n"/>
+      <c r="C99" s="3" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="n"/>
+    </row>
+    <row r="100" ht="49.95" customHeight="1">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="3" t="n"/>
+      <c r="C100" s="3" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n"/>
+    </row>
+    <row r="101" ht="49.95" customHeight="1">
+      <c r="A101" s="4" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+    </row>
+    <row r="102" ht="49.95" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>Neg_026</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Karunakarala mage CV eka check karanna.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>කරුණාකරලා මගේ CV එක check කරන්න.</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>කරුණාකරලා මගේ CV ඒක check කරන්න.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>UI Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="49.95" customHeight="1">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="3" t="n"/>
+      <c r="C103" s="3" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n"/>
+    </row>
+    <row r="104" ht="49.95" customHeight="1">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="3" t="n"/>
+      <c r="C104" s="3" t="n"/>
+      <c r="D104" s="3" t="n"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+    </row>
+    <row r="105" ht="49.95" customHeight="1">
+      <c r="A105" s="4" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="156">
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="D78:D81"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="F26:F29"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="C26:C29"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="B6:B9"/>
     <mergeCell ref="F6:F9"/>
-    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="F54:F57"/>
     <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -602,7 +602,7 @@
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>

--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -599,7 +599,11 @@
           <t>බත් කෑවට පස්සේ සෙල්ලම් කරන්න පුලුවන්ද?</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>බත් කෑවට පස්සේ සෙල්ලම් කරන්න පුළුවන්ද?</t>
+        </is>
+      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>UI Error</t>
@@ -651,7 +655,11 @@
           <t>ඉක්මනට ඇඳුමක් ඇද ගන්න ගමනක් යන්න, මං එද්දි ලෑස්ති වෙලා ඉන්න.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>ඉක්මනට ඇඳුමක් අඬා ගන්න ගමනක් යන්න, මං එද්දි ලෑස්ති වෙලා ඉන්න.</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>UI Error</t>
@@ -703,7 +711,11 @@
           <t>රෑට කෑම ඕනේ නම් පල්ලයහට එන්න</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>රට කෑම ඕනේ නම් පල්ලයහට එන්න</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>UI Error</t>
@@ -807,7 +819,11 @@
           <t>හොඳින් විභාගය කරන්න.</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>හොදින් විබාගය කරන්න.</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>UI Error</t>
